--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63273.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63273.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,13 +662,10 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
@@ -679,16 +676,10 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -696,7 +687,16 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -704,7 +704,15 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63273.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63273.xlsx
@@ -530,7 +530,11 @@
           <t>Prénom</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A a ho</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -538,7 +542,11 @@
           <t>Nom</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
